--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/aysen.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>111.37</v>
+        <v>113.48</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/aysen.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -572,6 +572,67 @@
         <v>113.48</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1057062-368-CM26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TRANSPORTES SURAY LIMITADA.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>77.799.670-3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2354.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/aysen.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -633,6 +633,128 @@
         <v>2354.36</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2713-1059-CM26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>11010</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1057062-420-CM26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TRANSPORTES SURAY LIMITADA.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>77.799.670-3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>14462.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
